--- a/EXCEL/Data/løn_data/løn_overenskosmt.xlsx
+++ b/EXCEL/Data/løn_data/løn_overenskosmt.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="41">
   <si>
     <t xml:space="preserve">Lønniveau - feb 2025 </t>
   </si>
@@ -25,6 +25,18 @@
     <t>Fuldtid</t>
   </si>
   <si>
+    <t>Lokale tillæg</t>
+  </si>
+  <si>
+    <t>Særydelser</t>
+  </si>
+  <si>
+    <t>Overarbejde</t>
+  </si>
+  <si>
+    <t>Nettoløn</t>
+  </si>
+  <si>
     <t>Bruttoløn</t>
   </si>
   <si>
@@ -73,7 +85,7 @@
     <t>Datasæt 02 2025</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 14.25.34</t>
+    <t>Kørsel 10.4.2026 10.34.27</t>
   </si>
   <si>
     <t/>
@@ -113,9 +125,6 @@
   </si>
   <si>
     <t>Lokalt aftalte tillæg</t>
-  </si>
-  <si>
-    <t>Særydelser</t>
   </si>
   <si>
     <t>Feriegodtgørelse</t>
@@ -573,24 +582,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
-    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="3" max="8" width="18" customWidth="1"/>
+    <col min="9" max="10" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -603,509 +616,845 @@
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5">
-        <v>18348.568462583782</v>
+        <v>18348.568462583793</v>
       </c>
       <c r="D3" s="6">
-        <v>47972.219061962416</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4516.462895892433</v>
+      </c>
+      <c r="E3" s="6">
+        <v>986.4277497798693</v>
+      </c>
+      <c r="F3" s="6">
+        <v>210.93676016727713</v>
+      </c>
+      <c r="G3" s="6">
+        <v>39258.849072598605</v>
+      </c>
+      <c r="H3" s="6">
+        <v>47977.60421123892</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" s="8">
-        <v>10614.16702849484</v>
+        <v>10614.167028494861</v>
       </c>
       <c r="D4" s="9">
-        <v>56686.41937180534</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6387.831044783449</v>
+      </c>
+      <c r="E4" s="9">
+        <v>35.72275506563278</v>
+      </c>
+      <c r="F4" s="9">
+        <v>27.938975699272042</v>
+      </c>
+      <c r="G4" s="9">
+        <v>46716.45130420734</v>
+      </c>
+      <c r="H4" s="9">
+        <v>56687.11505231534</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C5" s="5">
-        <v>1008.3607122103137</v>
+        <v>1008.3607122103139</v>
       </c>
       <c r="D5" s="6">
-        <v>55677.342135378414</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5159.298202351906</v>
+      </c>
+      <c r="E5" s="6">
+        <v>15.210045659118027</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>45909.54727414746</v>
+      </c>
+      <c r="H5" s="6">
+        <v>55677.34213537843</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C6" s="8">
-        <v>2529.5016684547336</v>
+        <v>2529.5016684547372</v>
       </c>
       <c r="D6" s="9">
-        <v>56281.820985298626</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5795.4231480938815</v>
+      </c>
+      <c r="E6" s="9">
+        <v>51.24065028997743</v>
+      </c>
+      <c r="F6" s="9">
+        <v>64.43538727643569</v>
+      </c>
+      <c r="G6" s="9">
+        <v>46379.16871334342</v>
+      </c>
+      <c r="H6" s="9">
+        <v>56283.42542647664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1895.447713411875</v>
+      </c>
+      <c r="D7" s="6">
+        <v>6645.596439966859</v>
+      </c>
+      <c r="E7" s="6">
+        <v>25.595956979998807</v>
+      </c>
+      <c r="F7" s="6">
+        <v>10.502578583438297</v>
+      </c>
+      <c r="G7" s="6">
+        <v>46899.062425472366</v>
+      </c>
+      <c r="H7" s="6">
+        <v>56902.21338169844</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="8">
+        <v>4109.032220512908</v>
+      </c>
+      <c r="D8" s="9">
+        <v>6407.123012803929</v>
+      </c>
+      <c r="E8" s="9">
+        <v>45.19335892585106</v>
+      </c>
+      <c r="F8" s="9">
+        <v>16.787734829632008</v>
+      </c>
+      <c r="G8" s="9">
+        <v>46616.19626892752</v>
+      </c>
+      <c r="H8" s="9">
+        <v>56591.817834252455</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1050.0042281908</v>
+      </c>
+      <c r="D9" s="6">
+        <v>8425.995707895934</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>42.543736462413996</v>
+      </c>
+      <c r="G9" s="6">
+        <v>48405.03988983135</v>
+      </c>
+      <c r="H9" s="6">
+        <v>58658.392178863716</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="8">
+        <v>21.82048571428572</v>
+      </c>
+      <c r="D10" s="9">
+        <v>7733.692650549874</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>44865.13514381853</v>
+      </c>
+      <c r="H10" s="9">
+        <v>54550.19217719495</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>1895.447713411876</v>
-      </c>
-      <c r="D7" s="6">
-        <v>56901.95186748589</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="8">
-        <v>4109.032220512913</v>
-      </c>
-      <c r="D8" s="9">
-        <v>56591.3998196459</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="C11" s="5">
+        <v>3288.371372610115</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1578.983872669794</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1882.3928225039997</v>
+      </c>
+      <c r="F11" s="6">
+        <v>188.36931639961645</v>
+      </c>
+      <c r="G11" s="6">
+        <v>28277.498141564716</v>
+      </c>
+      <c r="H11" s="6">
+        <v>34963.942896470086</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="5">
-        <v>1050.0042281907993</v>
-      </c>
-      <c r="D9" s="6">
-        <v>58657.3328398028</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="C12" s="8">
+        <v>30.926550170734586</v>
+      </c>
+      <c r="D12" s="9">
+        <v>2017.1661454510752</v>
+      </c>
+      <c r="E12" s="9">
+        <v>768.3341129422022</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>30028.749695263577</v>
+      </c>
+      <c r="H12" s="9">
+        <v>35809.757365544756</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="8">
-        <v>21.820485714285713</v>
-      </c>
-      <c r="D10" s="9">
-        <v>54550.192177194986</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="C13" s="5">
+        <v>1554.2716040465298</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1715.9145466436157</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1872.264297162671</v>
+      </c>
+      <c r="F13" s="6">
+        <v>204.09192057367488</v>
+      </c>
+      <c r="G13" s="6">
+        <v>27998.688298124067</v>
+      </c>
+      <c r="H13" s="6">
+        <v>34679.51045817295</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="5">
-        <v>3288.3713726101137</v>
-      </c>
-      <c r="D11" s="6">
-        <v>34958.426211884536</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="C14" s="8">
+        <v>454.01515010385975</v>
+      </c>
+      <c r="D14" s="9">
+        <v>1540.6580369510823</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1404.5501274422109</v>
+      </c>
+      <c r="F14" s="9">
+        <v>156.21555960523918</v>
+      </c>
+      <c r="G14" s="9">
+        <v>28650.36080162642</v>
+      </c>
+      <c r="H14" s="9">
+        <v>34875.59886827647</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="5">
+        <v>333.7713668529973</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1436.6133734858347</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1810.7963139625092</v>
+      </c>
+      <c r="F15" s="6">
+        <v>242.82183246841876</v>
+      </c>
+      <c r="G15" s="6">
+        <v>29397.587414113907</v>
+      </c>
+      <c r="H15" s="6">
+        <v>35920.37262297806</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="8">
+        <v>912.8242673748526</v>
+      </c>
+      <c r="D16" s="9">
+        <v>1404.6103644396576</v>
+      </c>
+      <c r="E16" s="9">
+        <v>2203.6867690315567</v>
+      </c>
+      <c r="F16" s="9">
+        <v>164.59113814783288</v>
+      </c>
+      <c r="G16" s="9">
+        <v>28097.01908808043</v>
+      </c>
+      <c r="H16" s="9">
+        <v>35115.55885973503</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2423.993198412553</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1873.1951987825084</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2926.6166686511447</v>
+      </c>
+      <c r="F17" s="6">
+        <v>812.9533491628629</v>
+      </c>
+      <c r="G17" s="6">
+        <v>29244.316432876734</v>
+      </c>
+      <c r="H17" s="6">
+        <v>36557.883579000096</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="8">
+        <v>306.051740553565</v>
+      </c>
+      <c r="D18" s="9">
+        <v>773.3278628759831</v>
+      </c>
+      <c r="E18" s="9">
+        <v>3055.090984672262</v>
+      </c>
+      <c r="F18" s="9">
+        <v>402.59132762306757</v>
+      </c>
+      <c r="G18" s="9">
+        <v>27698.49792581336</v>
+      </c>
+      <c r="H18" s="9">
+        <v>34795.56154420008</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="5">
+        <v>478.8051880898379</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1257.253430085301</v>
+      </c>
+      <c r="E19" s="6">
+        <v>3131.1358019966033</v>
+      </c>
+      <c r="F19" s="6">
+        <v>973.5342368553974</v>
+      </c>
+      <c r="G19" s="6">
+        <v>28369.429257740907</v>
+      </c>
+      <c r="H19" s="6">
+        <v>35752.32583319306</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="8">
-        <v>30.926550170734593</v>
-      </c>
-      <c r="D12" s="9">
-        <v>35809.75736554475</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="C20" s="8">
+        <v>483.04931887153555</v>
+      </c>
+      <c r="D20" s="9">
+        <v>1221.0325807718611</v>
+      </c>
+      <c r="E20" s="9">
+        <v>2842.843005817592</v>
+      </c>
+      <c r="F20" s="9">
+        <v>1133.2438246375314</v>
+      </c>
+      <c r="G20" s="9">
+        <v>28241.55890183131</v>
+      </c>
+      <c r="H20" s="9">
+        <v>35410.658609994876</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="5">
+        <v>403.29056689281504</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2186.575600296908</v>
+      </c>
+      <c r="E21" s="6">
+        <v>2986.9172500265754</v>
+      </c>
+      <c r="F21" s="6">
+        <v>1678.2156032500252</v>
+      </c>
+      <c r="G21" s="6">
+        <v>30140.534715800102</v>
+      </c>
+      <c r="H21" s="6">
+        <v>37651.76324644433</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="8">
+        <v>752.7963840047967</v>
+      </c>
+      <c r="D22" s="9">
+        <v>2962.7006653551593</v>
+      </c>
+      <c r="E22" s="9">
+        <v>2765.7545051327015</v>
+      </c>
+      <c r="F22" s="9">
+        <v>208.58919195688554</v>
+      </c>
+      <c r="G22" s="9">
+        <v>30592.550759801197</v>
+      </c>
+      <c r="H22" s="9">
+        <v>37936.85120543401</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="5">
+        <v>2022.0368630662933</v>
+      </c>
+      <c r="D23" s="6">
+        <v>2639.0345826457137</v>
+      </c>
+      <c r="E23" s="6">
+        <v>2193.958143679105</v>
+      </c>
+      <c r="F23" s="6">
+        <v>486.54749672157453</v>
+      </c>
+      <c r="G23" s="6">
+        <v>29975.973461839818</v>
+      </c>
+      <c r="H23" s="6">
+        <v>37112.754640836814</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="8">
+        <v>347.1855794289167</v>
+      </c>
+      <c r="D24" s="9">
+        <v>3451.8794587359043</v>
+      </c>
+      <c r="E24" s="9">
+        <v>2040.6943865208336</v>
+      </c>
+      <c r="F24" s="9">
+        <v>685.8849511835027</v>
+      </c>
+      <c r="G24" s="9">
+        <v>29370.649732694055</v>
+      </c>
+      <c r="H24" s="9">
+        <v>36107.90246933957</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="5">
+        <v>82.878267211288</v>
+      </c>
+      <c r="D25" s="6">
+        <v>2451.8826537786927</v>
+      </c>
+      <c r="E25" s="6">
+        <v>2089.1667022824504</v>
+      </c>
+      <c r="F25" s="6">
+        <v>79.43714934570245</v>
+      </c>
+      <c r="G25" s="6">
+        <v>28919.997241630772</v>
+      </c>
+      <c r="H25" s="6">
+        <v>35575.932384940155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1554.2716040465295</v>
-      </c>
-      <c r="D13" s="6">
-        <v>34673.55492705513</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="8">
-        <v>454.0151501038599</v>
-      </c>
-      <c r="D14" s="9">
-        <v>34871.00766524345</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="5">
-        <v>333.77136685299735</v>
-      </c>
-      <c r="D15" s="6">
-        <v>35913.233661018785</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="8">
-        <v>912.8242673748525</v>
-      </c>
-      <c r="D16" s="9">
-        <v>35110.7198802161</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="C26" s="8">
+        <v>474.6431693601674</v>
+      </c>
+      <c r="D26" s="9">
+        <v>2406.9754335724538</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1844.2043167895094</v>
+      </c>
+      <c r="F26" s="9">
+        <v>313.1167168680558</v>
+      </c>
+      <c r="G26" s="9">
+        <v>29268.04818301686</v>
+      </c>
+      <c r="H26" s="9">
+        <v>35951.21415359387</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="5">
-        <v>2423.9931984125515</v>
-      </c>
-      <c r="D17" s="6">
-        <v>36537.753029027335</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="8">
-        <v>306.05174055356525</v>
-      </c>
-      <c r="D18" s="9">
-        <v>34785.561031379606</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>478.80518808983766</v>
-      </c>
-      <c r="D19" s="6">
-        <v>35728.2122791065</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="8">
-        <v>483.0493188715353</v>
-      </c>
-      <c r="D20" s="9">
-        <v>35382.7172224387</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="5">
-        <v>403.29056689281487</v>
-      </c>
-      <c r="D21" s="6">
-        <v>37609.98090817727</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="8">
-        <v>752.7963840047968</v>
-      </c>
-      <c r="D22" s="9">
-        <v>37931.74696207191</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="C27" s="5">
+        <v>1024.0069726468876</v>
+      </c>
+      <c r="D27" s="6">
+        <v>2356.218887262209</v>
+      </c>
+      <c r="E27" s="6">
+        <v>2410.322742784251</v>
+      </c>
+      <c r="F27" s="6">
+        <v>555.5425011238667</v>
+      </c>
+      <c r="G27" s="6">
+        <v>30554.033990399956</v>
+      </c>
+      <c r="H27" s="6">
+        <v>38050.0063129441</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="5">
-        <v>2022.0368630662936</v>
-      </c>
-      <c r="D23" s="6">
-        <v>37100.64383929017</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="8">
-        <v>347.18557942891664</v>
-      </c>
-      <c r="D24" s="9">
-        <v>36091.02508774974</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="5">
-        <v>82.87826721128802</v>
-      </c>
-      <c r="D25" s="6">
-        <v>35573.954399878356</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="8">
-        <v>474.64316936016763</v>
-      </c>
-      <c r="D26" s="9">
-        <v>35943.41754717402</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>1024.0069726468878</v>
-      </c>
-      <c r="D27" s="6">
-        <v>38036.113459290245</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="C28" s="8">
         <v>91.322874419033</v>
       </c>
       <c r="D28" s="9">
-        <v>37922.10072603097</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4096.747366354874</v>
+      </c>
+      <c r="E28" s="9">
+        <v>2311.4886369396518</v>
+      </c>
+      <c r="F28" s="9">
+        <v>236.58794170102237</v>
+      </c>
+      <c r="G28" s="9">
+        <v>30454.83158671869</v>
+      </c>
+      <c r="H28" s="9">
+        <v>37927.99176590767</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B31" s="10"/>
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
